--- a/reports/operations/SENTINEL_RESOLUTION_WORKBENCH.xlsx
+++ b/reports/operations/SENTINEL_RESOLUTION_WORKBENCH.xlsx
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.9.5.161</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_report_architecture</t>
+          <t>v0.9.5.162_history_integrity_report_hygiene</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4780,11 +4780,11 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -4996,11 +4996,11 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -5212,11 +5212,11 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -5424,11 +5424,11 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -5640,11 +5640,11 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -5856,11 +5856,11 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -6072,11 +6072,11 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -6288,11 +6288,11 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -6504,11 +6504,11 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -6720,11 +6720,11 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
@@ -6936,11 +6936,11 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -7152,11 +7152,11 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
@@ -7368,11 +7368,11 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
@@ -7584,11 +7584,11 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
@@ -7776,11 +7776,11 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-07-23T21:18:17.102046+00:00</t>
+          <t>2026-07-23T21:40:44.108405+00:00</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12146,30 +12146,35 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>direct_strategy_match</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>strategy_alignment</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>simulation_only</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>automatic_fix_executed</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>gold_clearance_created</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ground_truth_used_as_evidence</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>operational_truth_modified</t>
         </is>
@@ -12178,7 +12183,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12257,7 +12262,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
         <v>0</v>
@@ -12266,13 +12271,16 @@
         <v>0</v>
       </c>
       <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12351,7 +12359,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -12360,13 +12368,16 @@
         <v>0</v>
       </c>
       <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12445,7 +12456,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
@@ -12454,13 +12465,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12539,7 +12553,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -12548,13 +12562,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12633,7 +12650,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -12642,13 +12659,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12727,7 +12747,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -12736,13 +12756,16 @@
         <v>0</v>
       </c>
       <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12821,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -12830,13 +12853,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12919,7 +12945,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -12928,13 +12954,16 @@
         <v>0</v>
       </c>
       <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -13013,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -13022,13 +13051,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -13107,7 +13139,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -13116,13 +13148,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13201,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -13210,13 +13245,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13295,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -13304,13 +13342,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13389,7 +13430,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -13398,13 +13439,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13483,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
@@ -13492,6 +13536,9 @@
         <v>0</v>
       </c>
       <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13624,7 +13671,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13706,7 +13753,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13788,7 +13835,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13870,7 +13917,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13952,7 +13999,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14034,7 +14081,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14116,7 +14163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14198,7 +14245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14280,7 +14327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14362,7 +14409,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -14444,7 +14491,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14526,7 +14573,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -14608,7 +14655,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14690,7 +14737,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -14772,7 +14819,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14854,7 +14901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -14936,7 +14983,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15018,7 +15065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15100,7 +15147,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -15182,7 +15229,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -15264,7 +15311,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -15346,7 +15393,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15428,7 +15475,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15510,7 +15557,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15592,7 +15639,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15674,7 +15721,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15756,7 +15803,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15838,7 +15885,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -15920,7 +15967,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -16002,7 +16049,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -16084,7 +16131,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -16166,7 +16213,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -16248,7 +16295,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -16330,7 +16377,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16412,7 +16459,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -16494,7 +16541,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16576,7 +16623,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16658,7 +16705,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16740,7 +16787,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16822,7 +16869,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16904,7 +16951,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -16986,7 +17033,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
